--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_374_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_374_R38.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.398</v>
+        <v>5.0282</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1743</v>
+        <v>2.6029</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2237</v>
+        <v>2.4253</v>
       </c>
       <c r="G2" t="n">
         <v>2.7433</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2731</v>
+        <v>-0.6429</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4402</v>
+        <v>-0.0116</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8329</v>
+        <v>-0.6313</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.384</v>
+        <v>3.5919</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8494</v>
+        <v>4.3213</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5346</v>
+        <v>-0.7295</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7802</v>
+        <v>4.1472</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4729</v>
+        <v>2.2233</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6926</v>
+        <v>1.9239</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8116</v>
+        <v>3.2608</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1329</v>
+        <v>1.1763</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3213</v>
+        <v>2.0844</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9686</v>
+        <v>0.8864</v>
       </c>
       <c r="N3" t="n">
-        <v>1.34</v>
+        <v>1.047</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3713</v>
+        <v>-0.1605</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0108</v>
+        <v>-0.411</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6948</v>
+        <v>-0.0116</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.3993</v>
       </c>
       <c r="V3" t="n">
-        <v>3.2166</v>
+        <v>-1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8223</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3943</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4397</v>
+        <v>3.4357</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9675</v>
+        <v>2.0295</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5278</v>
+        <v>1.4062</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1472</v>
+        <v>1.4013</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2233</v>
+        <v>3.5294</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9239</v>
+        <v>-2.128</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2608</v>
+        <v>0.6111</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1763</v>
+        <v>1.9998</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0844</v>
+        <v>-1.3887</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8864</v>
+        <v>0.7902</v>
       </c>
       <c r="N4" t="n">
-        <v>1.047</v>
+        <v>1.5296</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1605</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5632</v>
+        <v>-0.2851</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3655</v>
+        <v>0.3462</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1977</v>
+        <v>-0.6313</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1594</v>
+        <v>3.38</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9548</v>
+        <v>0.7446</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2046</v>
+        <v>2.6354</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4013</v>
+        <v>1.7802</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5294</v>
+        <v>2.4729</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.128</v>
+        <v>-0.6926</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6111</v>
+        <v>0.8116</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9998</v>
+        <v>1.1329</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3887</v>
+        <v>-0.3213</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7902</v>
+        <v>0.9686</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5296</v>
+        <v>1.34</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.3713</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3195</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5614</v>
+        <v>0.0068</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2715</v>
+        <v>0.59</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8329</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>2.8223</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4081</v>
+        <v>2.6508</v>
       </c>
       <c r="E6" t="n">
-        <v>1.46</v>
+        <v>1.5346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9482</v>
+        <v>1.1162</v>
       </c>
       <c r="G6" t="n">
         <v>1.9974</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.749</v>
+        <v>-0.5063</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4481</v>
+        <v>-0.3734</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3009</v>
+        <v>-0.1329</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9758</v>
+        <v>1.5383</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1842</v>
+        <v>1.9483</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2083</v>
+        <v>-0.41</v>
       </c>
       <c r="G7" t="n">
         <v>1.4253</v>
@@ -1000,13 +1000,13 @@
         <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6967</v>
+        <v>-1.1343</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1845</v>
+        <v>-0.4204</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5122</v>
+        <v>-0.7139</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.605</v>
+        <v>1.2421</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2984</v>
+        <v>-0.4596</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9034</v>
+        <v>1.7018</v>
       </c>
       <c r="G8" t="n">
         <v>0.06759999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2153</v>
+        <v>-0.1476</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1968</v>
+        <v>0.0356</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0185</v>
+        <v>-0.1832</v>
       </c>
       <c r="V8" t="n">
         <v>0.3943</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5778</v>
+        <v>0.8602</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.4917</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0104</v>
+        <v>0.3685</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0122</v>
+        <v>3.0007</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4093</v>
+        <v>2.6194</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4216</v>
+        <v>0.3814</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5881999999999999</v>
+        <v>4.5337</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5881999999999999</v>
+        <v>2.2554</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.2784</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6004</v>
+        <v>-1.533</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1788</v>
+        <v>0.364</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4216</v>
+        <v>-1.897</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>0.59</v>
+        <v>-1.4989</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.617</v>
       </c>
       <c r="U9" t="n">
-        <v>0.59</v>
+        <v>-0.8819</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5588</v>
+        <v>0.543</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.4301</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4825</v>
+        <v>0.1129</v>
       </c>
       <c r="G10" t="n">
         <v>0.7033</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0723</v>
+        <v>-1.0881</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>-0.4676</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2508</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1367</v>
+        <v>0.3425</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1379</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0012</v>
+        <v>-0.2457</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0007</v>
+        <v>-0.0122</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6194</v>
+        <v>0.4093</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3814</v>
+        <v>-0.4216</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5337</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2554</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>2.2784</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.533</v>
+        <v>-0.6004</v>
       </c>
       <c r="N11" t="n">
-        <v>0.364</v>
+        <v>-0.1788</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.897</v>
+        <v>-0.4216</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7834</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2224</v>
+        <v>0.3547</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9709</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2516</v>
+        <v>0.3547</v>
       </c>
       <c r="V11" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2968</v>
+        <v>-0.078</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.179</v>
+        <v>-0.061</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1178</v>
+        <v>-0.017</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9026</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0179</v>
+        <v>-0.7991</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6445</v>
+        <v>-0.5436</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9518</v>
+        <v>-1.7667</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3597</v>
+        <v>-0.2418</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5921</v>
+        <v>-1.5249</v>
       </c>
       <c r="G13" t="n">
         <v>0.7383</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6026</v>
+        <v>-1.4174</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8962</v>
+        <v>-0.7782</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7064</v>
+        <v>-0.6392</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.3947</v>
+        <v>20.768</v>
       </c>
       <c r="E14" t="n">
-        <v>13.5555</v>
+        <v>13.9288</v>
       </c>
       <c r="F14" t="n">
-        <v>6.839399999999999</v>
+        <v>6.839200000000001</v>
       </c>
       <c r="G14" t="n">
         <v>17.0898</v>
       </c>
       <c r="H14" t="n">
-        <v>22.61069999999999</v>
+        <v>22.6107</v>
       </c>
       <c r="I14" t="n">
         <v>-5.5206</v>
       </c>
       <c r="J14" t="n">
-        <v>18.8039</v>
+        <v>18.80390000000001</v>
       </c>
       <c r="K14" t="n">
         <v>14.8232</v>
@@ -1534,7 +1534,7 @@
         <v>7.7875</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.5015</v>
+        <v>-9.501499999999998</v>
       </c>
       <c r="P14" t="n">
         <v>6.958500000000001</v>
@@ -1546,13 +1546,13 @@
         <v>20.8757</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.942500000000001</v>
+        <v>-7.569199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3372</v>
+        <v>-1.9635</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.6054</v>
+        <v>-5.605599999999999</v>
       </c>
       <c r="V14" t="n">
         <v>4.2888</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6819</v>
+        <v>0.5525</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8254</v>
+        <v>2.4716</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1436</v>
+        <v>-1.9191</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1758</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7881</v>
+        <v>0.6587</v>
       </c>
       <c r="T15" t="n">
-        <v>0.767</v>
+        <v>0.4132</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0211</v>
+        <v>0.2456</v>
       </c>
       <c r="V15" t="n">
         <v>0.1418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.533</v>
+        <v>-0.2582</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5774</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0444</v>
+        <v>-0.1809</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3938</v>
+        <v>-0.1944</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6352</v>
+        <v>-1.3086</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2414</v>
+        <v>1.1142</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4532</v>
+        <v>1.5677</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2261</v>
+        <v>-0.3929</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7729</v>
+        <v>1.9606</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9405</v>
+        <v>-1.7621</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4091</v>
+        <v>-0.9157</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4685</v>
+        <v>-0.8464</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3031</v>
+        <v>1.4154</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1181</v>
+        <v>0.8496</v>
       </c>
       <c r="U16" t="n">
-        <v>0.185</v>
+        <v>0.5658</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>T. CARTER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2582</v>
+        <v>-0.8549</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.8113</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1809</v>
+        <v>-0.0436</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1944</v>
+        <v>-0.7615</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3086</v>
+        <v>-0.5942</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1142</v>
+        <v>-0.1673</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5677</v>
+        <v>0.25</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3929</v>
+        <v>-0.215</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9606</v>
+        <v>0.465</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7621</v>
+        <v>-1.0116</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9157</v>
+        <v>-0.3792</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8464</v>
+        <v>-0.6323</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.5515</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4154</v>
+        <v>0.3705</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8496</v>
+        <v>0.0984</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5658</v>
+        <v>0.2721</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9444</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.461</v>
+        <v>0.343</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4054</v>
+        <v>-1.3154</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0673</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.427</v>
+        <v>0.3991</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5702</v>
+        <v>0.4523</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1432</v>
+        <v>-0.0532</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5361</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RIVERO</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1563</v>
+        <v>-1.0412</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2806</v>
+        <v>0.4053</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4369</v>
+        <v>-1.4465</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.6926</v>
+        <v>-1.8227</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.5186</v>
+        <v>-1.9063</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.174</v>
+        <v>0.0835</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3054</v>
+        <v>0.3225</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.3422</v>
+        <v>0.2892</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>0.0333</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3871</v>
+        <v>-2.1452</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1763</v>
+        <v>-2.1954</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2108</v>
+        <v>0.0502</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5362</v>
+        <v>0.0857</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5138</v>
+        <v>0.0828</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0224</v>
+        <v>0.0029</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. CARTER</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3603</v>
+        <v>-1.0962</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2831</v>
+        <v>0.6901</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0772</v>
+        <v>-1.7863</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7615</v>
+        <v>-1.3938</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5942</v>
+        <v>-2.6352</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1673</v>
+        <v>1.2414</v>
       </c>
       <c r="J20" t="n">
-        <v>0.25</v>
+        <v>-0.4532</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.215</v>
+        <v>-1.2261</v>
       </c>
       <c r="L20" t="n">
-        <v>0.465</v>
+        <v>0.7729</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0116</v>
+        <v>-0.9405</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3792</v>
+        <v>-1.4091</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6323</v>
+        <v>0.4685</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1349</v>
+        <v>1.6739</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3734</v>
+        <v>1.2309</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2385</v>
+        <v>0.443</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>J. RIVERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5974</v>
+        <v>-1.8304</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1845</v>
+        <v>-0.4271</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4129</v>
+        <v>-1.4033</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8227</v>
+        <v>-3.6926</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9063</v>
+        <v>-3.5186</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0835</v>
+        <v>-0.174</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3225</v>
+        <v>-2.3054</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2892</v>
+        <v>-2.3422</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0333</v>
+        <v>0.0368</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1452</v>
+        <v>-1.3871</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.1954</v>
+        <v>-1.1763</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0502</v>
+        <v>-0.2108</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4705</v>
+        <v>0.8621</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.507</v>
+        <v>0.8061</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0365</v>
+        <v>0.056</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8701</v>
+        <v>-1.9037</v>
       </c>
       <c r="E22" t="n">
         <v>-1.0336</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8365</v>
+        <v>-0.8701</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1385</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1955</v>
+        <v>-0.2291</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1208</v>
+        <v>-0.1544</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9488</v>
+        <v>-2.3714</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.286</v>
+        <v>-2.1888</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3372</v>
+        <v>-0.1826</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3926</v>
+        <v>-0.6874</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0011</v>
+        <v>-1.0755</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3915</v>
+        <v>0.3881</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4101</v>
+        <v>-0.2941</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4271</v>
+        <v>-0.6855</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.017</v>
+        <v>0.3914</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8027</v>
+        <v>-0.3933</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.4282</v>
+        <v>-0.39</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3746</v>
+        <v>-0.0033</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0876</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2092</v>
+        <v>0.4758</v>
       </c>
       <c r="T23" t="n">
-        <v>1.3372</v>
+        <v>0.4248</v>
       </c>
       <c r="U23" t="n">
-        <v>0.872</v>
+        <v>0.051</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5052</v>
+        <v>-2.7985</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8965</v>
+        <v>-0.9483</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6087</v>
+        <v>-1.8502</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6874</v>
+        <v>-0.3033</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0755</v>
+        <v>-2.9532</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3881</v>
+        <v>2.65</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2941</v>
+        <v>1.3199</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6855</v>
+        <v>-1.2296</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3914</v>
+        <v>2.5495</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3933</v>
+        <v>-1.6231</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.39</v>
+        <v>-1.7236</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0033</v>
+        <v>0.1005</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6581</v>
+        <v>0.3451</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2829</v>
+        <v>0.0514</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3752</v>
+        <v>0.2937</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8987</v>
+        <v>-3.5126</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.656</v>
+        <v>-1.5051</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2427</v>
+        <v>-2.0075</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3033</v>
+        <v>-3.46</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.9532</v>
+        <v>-3.7611</v>
       </c>
       <c r="I25" t="n">
-        <v>2.65</v>
+        <v>0.3011</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3199</v>
+        <v>-1.1116</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.2296</v>
+        <v>-2.5201</v>
       </c>
       <c r="L25" t="n">
-        <v>2.5495</v>
+        <v>1.4085</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6231</v>
+        <v>-2.3484</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.7236</v>
+        <v>-1.241</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1005</v>
+        <v>-1.1074</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7552</v>
+        <v>1.035</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6563</v>
+        <v>0.4052</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0988</v>
+        <v>0.6297</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1444</v>
+        <v>0.5361</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X25" t="n">
         <v>-2.1444</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.0701</v>
+        <v>-3.5214</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5667</v>
+        <v>-3.7578</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5034</v>
+        <v>0.2363</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.46</v>
+        <v>-2.3926</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.7611</v>
+        <v>-2.0011</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3011</v>
+        <v>-0.3915</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.1116</v>
+        <v>0.4101</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.5201</v>
+        <v>0.4271</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4085</v>
+        <v>-0.017</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.3484</v>
+        <v>-2.8027</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.241</v>
+        <v>-2.4282</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.1074</v>
+        <v>-0.3746</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.6237</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.4793</v>
+        <v>-4.639</v>
       </c>
       <c r="R26" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4775</v>
+        <v>1.6366</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6563</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>1.1338</v>
+        <v>0.7712</v>
       </c>
       <c r="V26" t="n">
-        <v>0.5361</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>2.6805</v>
+        <v>-0.3943</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.1444</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-20.3946</v>
+        <v>-19.6083</v>
       </c>
       <c r="E27" t="n">
         <v>-6.8393</v>
       </c>
       <c r="F27" t="n">
-        <v>-13.5554</v>
+        <v>-12.7692</v>
       </c>
       <c r="G27" t="n">
         <v>-17.0899</v>
@@ -2530,13 +2530,13 @@
         <v>-22.6107</v>
       </c>
       <c r="I27" t="n">
-        <v>5.520799999999999</v>
+        <v>5.5208</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7141</v>
+        <v>1.714100000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.7873</v>
+        <v>-7.787299999999999</v>
       </c>
       <c r="L27" t="n">
         <v>9.5014</v>
@@ -2551,7 +2551,7 @@
         <v>-3.9809</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.958599999999999</v>
+        <v>-6.958600000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>-20.8757</v>
@@ -2560,19 +2560,19 @@
         <v>13.9174</v>
       </c>
       <c r="S27" t="n">
-        <v>7.9423</v>
+        <v>8.7288</v>
       </c>
       <c r="T27" t="n">
-        <v>5.605300000000001</v>
+        <v>5.6054</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3371</v>
+        <v>3.1234</v>
       </c>
       <c r="V27" t="n">
         <v>-4.2888</v>
       </c>
       <c r="W27" t="n">
-        <v>6.716799999999999</v>
+        <v>6.7168</v>
       </c>
       <c r="X27" t="n">
         <v>-11.0056</v>
